--- a/reports/pdf_rolling5_20260922.xlsx
+++ b/reports/pdf_rolling5_20260922.xlsx
@@ -569,7 +569,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,789억   ·   현금 53억(1.1%)      오늘 2026-09-22  vs  5일전 2026-09-15      매수 12종목  /  매도 16종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,789억   ·   현금 26억(0.6%)      오늘 2026-09-22  vs  5일전 2026-09-15      매수 12종목  /  매도 16종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -1054,23 +1054,23 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>ISC</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1386731779</v>
+        <v>2131290428</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>1.53%→1.83%</t>
+          <t>0.82%→1.15%</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>37→44</t>
+          <t>11→18</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -1098,23 +1098,23 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>ISC</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>2131290428</v>
+        <v>1386731779</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>0.82%→1.15%</t>
+          <t>1.53%→1.83%</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>11→18</t>
+          <t>37→44</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -1298,7 +1298,7 @@
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,325억   ·   현금 119억(3.5%)      오늘 2026-09-22  vs  5일전 2026-09-15      매수 0종목  /  매도 1종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,325억   ·   현금 59억(1.8%)      오늘 2026-09-22  vs  5일전 2026-09-15      매수 0종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B23" s="4" t="n"/>
@@ -1415,7 +1415,7 @@
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,616억   ·   현금 85억(3.2%)      오늘 2026-09-22  vs  5일전 2026-09-15      매수 4종목  /  매도 7종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,616억   ·   현금 43억(1.6%)      오늘 2026-09-22  vs  5일전 2026-09-15      매수 4종목  /  매도 7종목</t>
         </is>
       </c>
       <c r="B28" s="4" t="n"/>
@@ -1764,7 +1764,7 @@
     <row r="39" ht="19" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,005억   ·   현금 31억(1.5%)      오늘 2026-09-22  vs  5일전 2026-09-15      매수 4종목  /  매도 5종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,005억   ·   현금 15억(0.8%)      오늘 2026-09-22  vs  5일전 2026-09-15      매수 4종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B39" s="4" t="n"/>
@@ -2057,7 +2057,7 @@
     <row r="48" ht="19" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 289억   ·   현금 3억(0.9%)      오늘 2026-09-22  vs  5일전 2026-09-15      매수 9종목  /  매도 10종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 289억   ·   현금 1억(0.5%)      오늘 2026-09-22  vs  5일전 2026-09-15      매수 9종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B48" s="4" t="n"/>
@@ -2519,23 +2519,23 @@
       </c>
       <c r="G59" s="14" t="inlineStr">
         <is>
-          <t>오름테라퓨틱</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="H59" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-11466003</v>
+        <v>-54180015</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>0.15%→0.11%</t>
+          <t>2.45%→2.26%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
         <is>
-          <t>22→16</t>
+          <t>78→72</t>
         </is>
       </c>
     </row>
@@ -2547,23 +2547,23 @@
       <c r="E60" s="17" t="n"/>
       <c r="G60" s="14" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>오름테라퓨틱</t>
         </is>
       </c>
       <c r="H60" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-54180015</v>
+        <v>-11466003</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>2.45%→2.26%</t>
+          <t>0.15%→0.11%</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
         <is>
-          <t>78→72</t>
+          <t>22→16</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260922.xlsx
+++ b/reports/pdf_rolling5_20260922.xlsx
@@ -1054,23 +1054,23 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>ISC</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>2131290428</v>
+        <v>1386731779</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>0.82%→1.15%</t>
+          <t>1.53%→1.83%</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>11→18</t>
+          <t>37→44</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -1098,23 +1098,23 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>ISC</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1386731779</v>
+        <v>2131290428</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>1.53%→1.83%</t>
+          <t>0.82%→1.15%</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>37→44</t>
+          <t>11→18</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -2519,23 +2519,23 @@
       </c>
       <c r="G59" s="14" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>오름테라퓨틱</t>
         </is>
       </c>
       <c r="H59" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-54180015</v>
+        <v>-11466003</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>2.45%→2.26%</t>
+          <t>0.15%→0.11%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
         <is>
-          <t>78→72</t>
+          <t>22→16</t>
         </is>
       </c>
     </row>
@@ -2547,23 +2547,23 @@
       <c r="E60" s="17" t="n"/>
       <c r="G60" s="14" t="inlineStr">
         <is>
-          <t>오름테라퓨틱</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="H60" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-11466003</v>
+        <v>-54180015</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>0.15%→0.11%</t>
+          <t>2.45%→2.26%</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
         <is>
-          <t>22→16</t>
+          <t>78→72</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260922.xlsx
+++ b/reports/pdf_rolling5_20260922.xlsx
@@ -1163,23 +1163,23 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>코나아이</t>
+          <t>씨메스로보틱스</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-453123091</v>
+        <v>-221128844</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>1.25%→1.04%</t>
+          <t>0.20%→0.14%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>143→131</t>
+          <t>49→37</t>
         </is>
       </c>
     </row>
@@ -1191,23 +1191,23 @@
       <c r="E18" s="17" t="n"/>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>씨메스로보틱스</t>
+          <t>코나아이</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-221128844</v>
+        <v>-453123091</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.20%→0.14%</t>
+          <t>1.25%→1.04%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>49→37</t>
+          <t>143→131</t>
         </is>
       </c>
     </row>
@@ -1685,23 +1685,23 @@
       <c r="E35" s="17" t="n"/>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H35" s="15" t="n">
         <v>-16</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-2239127671</v>
+        <v>-1197470224</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>6.10%→4.84%</t>
+          <t>0.79%→0.41%</t>
         </is>
       </c>
       <c r="K35" s="13" t="inlineStr">
         <is>
-          <t>105→89</t>
+          <t>30→14</t>
         </is>
       </c>
     </row>
@@ -1713,23 +1713,23 @@
       <c r="E36" s="17" t="n"/>
       <c r="G36" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H36" s="15" t="n">
         <v>-16</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-1197470224</v>
+        <v>-2239127671</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
-          <t>0.79%→0.41%</t>
+          <t>6.10%→4.84%</t>
         </is>
       </c>
       <c r="K36" s="13" t="inlineStr">
         <is>
-          <t>30→14</t>
+          <t>105→89</t>
         </is>
       </c>
     </row>
@@ -2519,23 +2519,23 @@
       </c>
       <c r="G59" s="14" t="inlineStr">
         <is>
-          <t>오름테라퓨틱</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="H59" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-11466003</v>
+        <v>-54180015</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>0.15%→0.11%</t>
+          <t>2.45%→2.26%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
         <is>
-          <t>22→16</t>
+          <t>78→72</t>
         </is>
       </c>
     </row>
@@ -2547,23 +2547,23 @@
       <c r="E60" s="17" t="n"/>
       <c r="G60" s="14" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>오름테라퓨틱</t>
         </is>
       </c>
       <c r="H60" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-54180015</v>
+        <v>-11466003</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>2.45%→2.26%</t>
+          <t>0.15%→0.11%</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
         <is>
-          <t>78→72</t>
+          <t>22→16</t>
         </is>
       </c>
     </row>
